--- a/output/roomself_excel/7080.xlsx
+++ b/output/roomself_excel/7080.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131544</v>
+        <v>84537</v>
       </c>
       <c r="D2" t="n">
-        <v>2904</v>
+        <v>2656</v>
       </c>
       <c r="E2" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="F2" t="n">
-        <v>404</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30622</v>
+        <v>188332</v>
       </c>
       <c r="D3" t="n">
-        <v>1468</v>
+        <v>3584</v>
       </c>
       <c r="E3" t="n">
-        <v>208</v>
+        <v>564</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>310929</v>
+        <v>131544</v>
       </c>
       <c r="D4" t="n">
-        <v>6640</v>
+        <v>2904</v>
       </c>
       <c r="E4" t="n">
-        <v>785</v>
+        <v>408</v>
       </c>
       <c r="F4" t="n">
-        <v>589</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,63 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30622</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1468</v>
+      </c>
+      <c r="E5" t="n">
+        <v>208</v>
+      </c>
+      <c r="F5" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38060</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1584</v>
+      </c>
+      <c r="E6" t="n">
+        <v>133</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C7" t="n">
         <v>18928</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>1144</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E7" t="n">
         <v>162</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F7" t="n">
         <v>149</v>
       </c>
     </row>

--- a/output/roomself_excel/7080.xlsx
+++ b/output/roomself_excel/7080.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,11 +525,49 @@
       <c r="D2" t="n">
         <v>2656</v>
       </c>
-      <c r="E2" t="n">
-        <v>489</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>199</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>36</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>59</v>
+      </c>
+      <c r="M2" t="n">
+        <v>55</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>375</v>
+      </c>
+      <c r="P2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +585,34 @@
       <c r="D3" t="n">
         <v>3584</v>
       </c>
-      <c r="E3" t="n">
-        <v>564</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>390</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>358</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +629,42 @@
       <c r="D4" t="n">
         <v>2904</v>
       </c>
-      <c r="E4" t="n">
-        <v>408</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>404</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>348</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>378</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +681,34 @@
       <c r="D5" t="n">
         <v>1468</v>
       </c>
-      <c r="E5" t="n">
-        <v>208</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>138</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>70</v>
+      </c>
+      <c r="J5" t="n">
         <v>65</v>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +725,26 @@
       <c r="D6" t="n">
         <v>1584</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>133</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>26</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +761,34 @@
       <c r="D7" t="n">
         <v>1144</v>
       </c>
-      <c r="E7" t="n">
-        <v>162</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>149</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>94</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
